--- a/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
+++ b/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
@@ -1,50 +1,189 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22730"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8f5fb949e079843e/Documents/GitHub/apache-fineract-manual-qa/02_Test_Plan/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{17BC1B88-233B-48FB-9919-D2DF374B6B28}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Plan" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Test Plan" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+  <si>
+    <t>Apache Fineract Test Plan</t>
+  </si>
+  <si>
+    <t>Project Name</t>
+  </si>
+  <si>
+    <t>Apache Fineract Manual QA</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>Version</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>Prepared By</t>
+  </si>
+  <si>
+    <t>Sachin</t>
+  </si>
+  <si>
+    <t>Objective</t>
+  </si>
+  <si>
+    <t>Define the testing approach for the Login module of Apache Fineract.</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Login &amp; Authentication functionality</t>
+  </si>
+  <si>
+    <t>In Scope</t>
+  </si>
+  <si>
+    <t>Valid/Invalid Login, Validation, Logout, Session Timeout</t>
+  </si>
+  <si>
+    <t>Out of Scope</t>
+  </si>
+  <si>
+    <t>Registration, Forgot Password, MFA</t>
+  </si>
+  <si>
+    <t>Test Types</t>
+  </si>
+  <si>
+    <t>Smoke, Functional, Regression, System, UAT</t>
+  </si>
+  <si>
+    <t>Entry Criteria</t>
+  </si>
+  <si>
+    <t>BRD approved, Test environment available</t>
+  </si>
+  <si>
+    <t>Exit Criteria</t>
+  </si>
+  <si>
+    <t>All critical defects closed, test execution completed</t>
+  </si>
+  <si>
+    <t>Deliverables</t>
+  </si>
+  <si>
+    <t>Test Cases, Test Scenarios, Bug Report, RTM, Execution Report</t>
+  </si>
+  <si>
+    <t>Risks</t>
+  </si>
+  <si>
+    <t>Environment downtime, requirement changes</t>
+  </si>
+  <si>
+    <t>Assumptions</t>
+  </si>
+  <si>
+    <t>Stable application and test environment</t>
+  </si>
+  <si>
+    <t>Application Name</t>
+  </si>
+  <si>
+    <t>Apache Fineract</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>Banking</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Manual QA Engineer</t>
+  </si>
+  <si>
+    <t>Reviewed By</t>
+  </si>
+  <si>
+    <t>QA Lead (TBD)</t>
+  </si>
+  <si>
+    <t>Approved By</t>
+  </si>
+  <si>
+    <t>Test Manager (TBD)</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Draft</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
       <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,83 +199,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -424,199 +516,233 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Apache Fineract Test Plan</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Project Name</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Apache Fineract Manual QA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Login</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Version</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Prepared By</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Sachin</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Objective</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Define the testing approach for the Login module of Apache Fineract.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Login &amp; Authentication functionality</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>In Scope</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Valid/Invalid Login, Validation, Logout, Session Timeout</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Out of Scope</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Registration, Forgot Password, MFA</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Test Types</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Smoke, Functional, Regression, System, UAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Entry Criteria</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>BRD approved, Test environment available</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Exit Criteria</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>All critical defects closed, test execution completed</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Deliverables</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Test Cases, Test Scenarios, Bug Report, RTM, Execution Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>Risks</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Environment downtime, requirement changes</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Assumptions</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Stable application and test environment</t>
-        </is>
+    <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="6">
+        <v>46236</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF7177D2-9E5F-4C4B-B72F-95C8FC900A70}">
+  <dimension ref="A1:A10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="69.85546875" customWidth="1"/>
+    <col min="2" max="2" width="50.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2"/>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
+++ b/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8f5fb949e079843e/Documents/GitHub/apache-fineract-manual-qa/02_Test_Plan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{17BC1B88-233B-48FB-9919-D2DF374B6B28}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{8D5744B6-CF63-48B1-A2D5-9B9187E3967C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,10 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
-  <si>
-    <t>Apache Fineract Test Plan</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Project Name</t>
   </si>
@@ -41,9 +38,6 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0</t>
-  </si>
-  <si>
     <t>Prepared By</t>
   </si>
   <si>
@@ -53,15 +47,9 @@
     <t>Objective</t>
   </si>
   <si>
-    <t>Define the testing approach for the Login module of Apache Fineract.</t>
-  </si>
-  <si>
     <t>Scope</t>
   </si>
   <si>
-    <t>Login &amp; Authentication functionality</t>
-  </si>
-  <si>
     <t>In Scope</t>
   </si>
   <si>
@@ -147,13 +135,22 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>Apache Fineract Manual QA Test Plan</t>
+  </si>
+  <si>
+    <t>To verify that the Apache Fineract Login module functions correctly by validating authentication, authorization, input validation, session management, and security requirements, ensuring that only authorized users can securely access the application.</t>
+  </si>
+  <si>
+    <t>This test plan covers the manual functional testing of the Apache Fineract Login module, including user authentication, authorization, field validation, session management, logout functionality, and related security validations.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -163,14 +160,22 @@
     </font>
     <font>
       <b/>
-      <sz val="14"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -182,12 +187,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF1F4E78"/>
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -195,25 +200,128 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -520,186 +628,190 @@
   <dimension ref="A1:B22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="33.85546875" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="3"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="4" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="B4" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="8">
+        <v>46236</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B13" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="5" t="s">
+      <c r="B14" s="9" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" s="6">
-        <v>46236</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+    <row r="22" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B22" s="11" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -713,34 +825,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2"/>
+      <c r="A1" s="1"/>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
+      <c r="A2" s="1"/>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2"/>
+      <c r="A3" s="1"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
+      <c r="A4" s="1"/>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2"/>
+      <c r="A5" s="1"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
+      <c r="A6" s="1"/>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
+      <c r="A7" s="1"/>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2"/>
+      <c r="A8" s="1"/>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2"/>
+      <c r="A9" s="1"/>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
+      <c r="A10" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
+++ b/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8f5fb949e079843e/Documents/GitHub/apache-fineract-manual-qa/02_Test_Plan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{8D5744B6-CF63-48B1-A2D5-9B9187E3967C}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{DEC11938-7826-471D-896A-FEDE040FB21A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,9 +53,6 @@
     <t>In Scope</t>
   </si>
   <si>
-    <t>Valid/Invalid Login, Validation, Logout, Session Timeout</t>
-  </si>
-  <si>
     <t>Out of Scope</t>
   </si>
   <si>
@@ -144,6 +141,16 @@
   </si>
   <si>
     <t>This test plan covers the manual functional testing of the Apache Fineract Login module, including user authentication, authorization, field validation, session management, logout functionality, and related security validations.</t>
+  </si>
+  <si>
+    <t>User Login - Verify login using valid credentials
+Invalid Login - Verify login using invalid credentials
+Mandatory Field Validation - Verify username and password are mandatory
+Password Masking - Verify password is hidden while typing
+User Authentication - Verify only authorized users can access the application
+Session Management - Verify user session timeout after inactivity
+Logout Functionality - Verify users can securely log out of the application
+Error Message Validation - Verify appropriate error messages are displayed for invalid login attempts</t>
   </si>
 </sst>
 </file>
@@ -294,15 +301,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -322,6 +323,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -629,181 +639,181 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.85546875" customWidth="1"/>
-    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="2" max="2" width="98.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="11"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="6">
+        <v>46236</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="3"/>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="8">
-        <v>46236</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="9" t="s">
+    </row>
+    <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="9" t="s">
+    <row r="15" spans="1:2" ht="120" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="5" t="s">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B16" s="5" t="s">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="5" t="s">
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="5" t="s">
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="5" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="5" t="s">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="5" t="s">
+    </row>
+    <row r="22" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
+      <c r="B22" s="9" t="s">
         <v>23</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
+++ b/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8f5fb949e079843e/Documents/GitHub/apache-fineract-manual-qa/02_Test_Plan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="47" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{DEC11938-7826-471D-896A-FEDE040FB21A}"/>
+  <xr:revisionPtr revIDLastSave="49" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{8B2297E4-0282-42CF-87C4-C6F5EDD6896D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -736,7 +736,7 @@
         <v>46236</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>7</v>
       </c>

--- a/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
+++ b/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8f5fb949e079843e/Documents/GitHub/apache-fineract-manual-qa/02_Test_Plan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{8B2297E4-0282-42CF-87C4-C6F5EDD6896D}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{55736987-7D45-4E09-A467-C9185E98EE0F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,9 +56,6 @@
     <t>Out of Scope</t>
   </si>
   <si>
-    <t>Registration, Forgot Password, MFA</t>
-  </si>
-  <si>
     <t>Test Types</t>
   </si>
   <si>
@@ -151,6 +148,13 @@
 Session Management - Verify user session timeout after inactivity
 Logout Functionality - Verify users can securely log out of the application
 Error Message Validation - Verify appropriate error messages are displayed for invalid login attempts</t>
+  </si>
+  <si>
+    <t>User Registration - New user registration is not covered in this testing cycle
+Forgot Password - Password reset functionality is not included in this testing cycle
+Multi-Factor Authentication (MFA) - MFA functionality is not part of the current release
+User Profile Management - Profile update functionality is not included in this testing cycle
+Performance and Load Testing - Performance testing is excluded from the scope of this manual testing cycle</t>
   </si>
 </sst>
 </file>
@@ -324,14 +328,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -643,10 +647,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="11"/>
+      <c r="A1" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="12"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -682,55 +686,55 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B12" s="6">
         <v>46236</v>
@@ -741,7 +745,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -749,71 +753,71 @@
         <v>8</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>11</v>
+      <c r="B16" s="10" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>22</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
+++ b/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8f5fb949e079843e/Documents/GitHub/apache-fineract-manual-qa/02_Test_Plan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="51" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{55736987-7D45-4E09-A467-C9185E98EE0F}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{E8156BE1-CDCE-401B-BC36-76AA459EC2EF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,9 +59,6 @@
     <t>Test Types</t>
   </si>
   <si>
-    <t>Smoke, Functional, Regression, System, UAT</t>
-  </si>
-  <si>
     <t>Entry Criteria</t>
   </si>
   <si>
@@ -155,6 +152,13 @@
 Multi-Factor Authentication (MFA) - MFA functionality is not part of the current release
 User Profile Management - Profile update functionality is not included in this testing cycle
 Performance and Load Testing - Performance testing is excluded from the scope of this manual testing cycle</t>
+  </si>
+  <si>
+    <t>Smoke Testing – Verify that the critical login functionality is working correctly before detailed testing begins.
+Functional Testing – Verify that all login features work according to the business requirements and functional specifications.
+Regression Testing – Verify that existing login functionality continues to work correctly after new changes, enhancements, or bug fixes.
+System Testing – Verify that the complete Login module functions correctly within the Apache Fineract application and integrates properly with related components.
+User Acceptance Testing (UAT) – Support business users in validating that the Login module meets business requirements and is ready for production use.</t>
   </si>
 </sst>
 </file>
@@ -305,7 +309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -336,6 +340,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -643,12 +650,12 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.85546875" customWidth="1"/>
-    <col min="2" max="2" width="98.85546875" customWidth="1"/>
+    <col min="2" max="2" width="111.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B1" s="12"/>
     </row>
@@ -686,55 +693,55 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="6">
         <v>46236</v>
@@ -745,7 +752,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -753,7 +760,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -761,7 +768,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -769,55 +776,55 @@
         <v>10</v>
       </c>
       <c r="B16" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="135" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>40</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>13</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>21</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
+++ b/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8f5fb949e079843e/Documents/GitHub/apache-fineract-manual-qa/02_Test_Plan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{E8156BE1-CDCE-401B-BC36-76AA459EC2EF}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{DECADE49-C697-4AC1-9A81-92A5E5B67B28}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>Project Name</t>
   </si>
@@ -159,6 +159,16 @@
 Regression Testing – Verify that existing login functionality continues to work correctly after new changes, enhancements, or bug fixes.
 System Testing – Verify that the complete Login module functions correctly within the Apache Fineract application and integrates properly with related components.
 User Acceptance Testing (UAT) – Support business users in validating that the Login module meets business requirements and is ready for production use.</t>
+  </si>
+  <si>
+    <t>Test Environment</t>
+  </si>
+  <si>
+    <t>Application: Apache Fineract
+Environment: QA / Test Environment
+Browser: Google Chrome (Latest Stable Version)
+Database: MySQL
+Test Data: Dedicated QA test accounts and sample banking data</t>
   </si>
 </sst>
 </file>
@@ -646,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.85546875" customWidth="1"/>
@@ -787,43 +797,51 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>13</v>
+    <row r="18" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="8" t="s">
+    <row r="23" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B23" s="9" t="s">
         <v>21</v>
       </c>
     </row>

--- a/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
+++ b/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8f5fb949e079843e/Documents/GitHub/apache-fineract-manual-qa/02_Test_Plan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{DECADE49-C697-4AC1-9A81-92A5E5B67B28}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{01C52E2B-E69D-496D-8B80-4F59CB2DB753}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,9 +62,6 @@
     <t>Entry Criteria</t>
   </si>
   <si>
-    <t>BRD approved, Test environment available</t>
-  </si>
-  <si>
     <t>Exit Criteria</t>
   </si>
   <si>
@@ -169,6 +166,13 @@
 Browser: Google Chrome (Latest Stable Version)
 Database: MySQL
 Test Data: Dedicated QA test accounts and sample banking data</t>
+  </si>
+  <si>
+    <t>Business Requirements Document (BRD) is reviewed and approved.
+Test environment is configured and accessible.
+A stable application build is available for testing.
+Required test data and test user accounts are available.
+All required access permissions are granted to the QA team.</t>
   </si>
 </sst>
 </file>
@@ -665,7 +669,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B1" s="12"/>
     </row>
@@ -703,55 +707,55 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="6">
         <v>46236</v>
@@ -762,7 +766,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -770,7 +774,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -778,7 +782,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -786,7 +790,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -794,55 +798,55 @@
         <v>11</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>13</v>
+      <c r="B19" s="10" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>14</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
+++ b/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8f5fb949e079843e/Documents/GitHub/apache-fineract-manual-qa/02_Test_Plan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{01C52E2B-E69D-496D-8B80-4F59CB2DB753}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{B92B613A-4B39-4E32-95C6-B742B68699CD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,9 +65,6 @@
     <t>Exit Criteria</t>
   </si>
   <si>
-    <t>All critical defects closed, test execution completed</t>
-  </si>
-  <si>
     <t>Deliverables</t>
   </si>
   <si>
@@ -173,6 +170,13 @@
 A stable application build is available for testing.
 Required test data and test user accounts are available.
 All required access permissions are granted to the QA team.</t>
+  </si>
+  <si>
+    <t>All planned test cases have been executed.
+All Critical and High severity defects are closed or accepted by stakeholders.
+No open Blocker defects remain.
+Test Summary Report is prepared and shared with stakeholders.
+Business stakeholders approve the application for release or provide formal sign-off for the completed testing cycle.</t>
   </si>
 </sst>
 </file>
@@ -669,7 +673,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B1" s="12"/>
     </row>
@@ -707,55 +711,55 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>31</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" s="6">
         <v>46236</v>
@@ -766,7 +770,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -774,7 +778,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -782,7 +786,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -790,7 +794,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -798,15 +802,15 @@
         <v>11</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>40</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -814,39 +818,39 @@
         <v>12</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>14</v>
+      <c r="B20" s="10" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>19</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
+++ b/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8f5fb949e079843e/Documents/GitHub/apache-fineract-manual-qa/02_Test_Plan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{B92B613A-4B39-4E32-95C6-B742B68699CD}"/>
+  <xr:revisionPtr revIDLastSave="81" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{4684F12C-299B-4731-A3C1-8E6F4322221C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -68,9 +68,6 @@
     <t>Deliverables</t>
   </si>
   <si>
-    <t>Test Cases, Test Scenarios, Bug Report, RTM, Execution Report</t>
-  </si>
-  <si>
     <t>Risks</t>
   </si>
   <si>
@@ -177,6 +174,20 @@
 No open Blocker defects remain.
 Test Summary Report is prepared and shared with stakeholders.
 Business stakeholders approve the application for release or provide formal sign-off for the completed testing cycle.</t>
+  </si>
+  <si>
+    <t>Business Requirements Document (BRD)
+Test Plan
+Test Scenarios
+Test Cases
+Test Data
+Requirement Traceability Matrix (RTM)
+Bug / Defect Report
+Test Execution Report
+SQL Validation Scripts
+API Test Collection (Postman)
+Test Summary Report
+Release Sign-off Document</t>
   </si>
 </sst>
 </file>
@@ -673,7 +684,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B1" s="12"/>
     </row>
@@ -711,55 +722,55 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>24</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B12" s="6">
         <v>46236</v>
@@ -770,7 +781,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -778,7 +789,7 @@
         <v>8</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="120" x14ac:dyDescent="0.25">
@@ -786,7 +797,7 @@
         <v>9</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -794,7 +805,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="135" x14ac:dyDescent="0.25">
@@ -802,15 +813,15 @@
         <v>11</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="10" t="s">
         <v>39</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -818,7 +829,7 @@
         <v>12</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -826,31 +837,31 @@
         <v>13</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="345" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>15</v>
+      <c r="B21" s="10" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>18</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
+++ b/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8f5fb949e079843e/Documents/GitHub/apache-fineract-manual-qa/02_Test_Plan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{4684F12C-299B-4731-A3C1-8E6F4322221C}"/>
+  <xr:revisionPtr revIDLastSave="85" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{2BC04741-2FFD-4520-A624-C0723DC5D85B}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -71,13 +71,7 @@
     <t>Risks</t>
   </si>
   <si>
-    <t>Environment downtime, requirement changes</t>
-  </si>
-  <si>
     <t>Assumptions</t>
-  </si>
-  <si>
-    <t>Stable application and test environment</t>
   </si>
   <si>
     <t>Application Name</t>
@@ -188,6 +182,23 @@
 API Test Collection (Postman)
 Test Summary Report
 Release Sign-off Document</t>
+  </si>
+  <si>
+    <t>Requirement changes during the testing cycle.
+Test environment unavailability or instability.
+Delay in receiving application builds.
+Insufficient or incorrect test data.
+High-priority defects delaying test execution.
+Dependency on external systems or third-party services.
+Resource availability due to leave or workload.</t>
+  </si>
+  <si>
+    <t>Business requirements are complete and approved.
+The QA environment will remain available throughout testing.
+Valid test user accounts and test data are available.
+The application build provided for testing is stable.
+Required access to tools and environments is available.
+Stakeholders are available for requirement clarifications when needed.</t>
   </si>
 </sst>
 </file>
@@ -358,9 +369,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -372,6 +380,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -683,10 +694,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="12"/>
+      <c r="A1" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="11"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -722,55 +733,55 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B12" s="6">
         <v>46236</v>
@@ -781,7 +792,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.25">
@@ -789,79 +800,79 @@
         <v>8</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="120" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>35</v>
+      <c r="B15" s="9" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="135" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="75" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="135" x14ac:dyDescent="0.25">
-      <c r="A17" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B17" s="10" t="s">
+      <c r="B18" s="9" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A18" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>40</v>
+      <c r="B19" s="9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>41</v>
+      <c r="B20" s="9" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="345" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="195" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>18</v>
+      <c r="B23" s="13" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
+++ b/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8f5fb949e079843e/Documents/GitHub/apache-fineract-manual-qa/02_Test_Plan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="85" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{2BC04741-2FFD-4520-A624-C0723DC5D85B}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{877BE3FE-9C6A-4FA3-82F9-75E057A1DAF2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>Project Name</t>
   </si>
@@ -199,6 +199,68 @@
 The application build provided for testing is stable.
 Required access to tools and environments is available.
 Stakeholders are available for requirement clarifications when needed.</t>
+  </si>
+  <si>
+    <t>Roles &amp; Responsibilities</t>
+  </si>
+  <si>
+    <t>Business Analyst (BA)
+• Prepare and maintain business requirements.
+• Clarify functional requirements.
+QA Engineer
+• Analyze requirements.
+• Create test scenarios and test cases.
+• Execute test cases.
+• Report and verify defects.
+• Prepare test reports.
+Developer
+• Fix reported defects.
+• Support defect analysis.
+QA Lead
+• Review test artifacts.
+• Monitor testing progress.
+• Approve test deliverables.
+Project Manager
+• Monitor project timelines.
+• Coordinate between teams.
+• Approve project milestones.</t>
+  </si>
+  <si>
+    <t>Test Schedule</t>
+  </si>
+  <si>
+    <t>Requirement Analysis
+• Review Business Requirements Document (BRD).
+Test Planning
+• Prepare and review the Test Plan.
+Test Design
+• Create Test Scenarios and Test Cases.
+Test Data Preparation
+• Prepare test users and sample banking data.
+Test Execution
+• Execute planned test cases and record results.
+Defect Reporting
+• Log, track, and verify reported defects.
+Regression Testing
+• Re-test resolved defects and impacted functionality.
+Test Closure
+• Prepare the Test Summary Report and obtain sign-off.</t>
+  </si>
+  <si>
+    <t>Approval / Sign-off</t>
+  </si>
+  <si>
+    <t>Prepared By
+• Sachin Kodase
+• Manual QA Engineer
+Reviewed By
+• QA Lead
+• To Be Assigned (TBD)
+Approved By
+• Test Manager / Project Manager
+• To Be Assigned (TBD)
+Document Status
+• Draft (Version 1.0)</t>
   </si>
 </sst>
 </file>
@@ -247,7 +309,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -256,37 +318,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -300,90 +332,39 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -686,7 +667,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.85546875" customWidth="1"/>
@@ -694,117 +675,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="11"/>
+      <c r="B1" s="2"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="7">
         <v>46236</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+    <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="8" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="120" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="9" t="s">
@@ -812,7 +793,7 @@
       </c>
     </row>
     <row r="16" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B16" s="9" t="s">
@@ -820,7 +801,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" ht="135" x14ac:dyDescent="0.25">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B17" s="9" t="s">
@@ -828,7 +809,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A18" s="12" t="s">
+      <c r="A18" s="10" t="s">
         <v>36</v>
       </c>
       <c r="B18" s="9" t="s">
@@ -836,7 +817,7 @@
       </c>
     </row>
     <row r="19" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B19" s="9" t="s">
@@ -844,7 +825,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="9" t="s">
@@ -852,7 +833,7 @@
       </c>
     </row>
     <row r="21" spans="1:2" ht="345" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B21" s="9" t="s">
@@ -860,19 +841,43 @@
       </c>
     </row>
     <row r="22" spans="1:2" ht="195" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B22" s="9" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="8" t="s">
+    <row r="23" spans="1:2" ht="165" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="9" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="360" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="345" x14ac:dyDescent="0.25">
+      <c r="A25" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="210" x14ac:dyDescent="0.25">
+      <c r="A26" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
+++ b/02_Test_Plan/Apache_Fineract_Test_Plan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8f5fb949e079843e/Documents/GitHub/apache-fineract-manual-qa/02_Test_Plan/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{877BE3FE-9C6A-4FA3-82F9-75E057A1DAF2}"/>
+  <xr:revisionPtr revIDLastSave="98" documentId="11_E94D148F576A487F601A04964CB306FF4B2389CD" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{09345EEC-9E77-4100-80FC-796E1345A59E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -336,16 +336,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -356,15 +349,23 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -675,128 +676,128 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="2"/>
+      <c r="B1" s="6"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="8" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="8" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="3" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="3" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="4">
         <v>46236</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="9" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="120" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="3" t="s">
         <v>34</v>
       </c>
     </row>
@@ -804,7 +805,7 @@
       <c r="A17" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="3" t="s">
         <v>35</v>
       </c>
     </row>
@@ -812,71 +813,71 @@
       <c r="A18" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="3" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" s="3" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="75" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="3" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="345" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" s="3" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="195" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="165" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="3" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="360" x14ac:dyDescent="0.25">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="9" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="345" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="9" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="210" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="9" t="s">
         <v>48</v>
       </c>
     </row>
